--- a/artfynd/A 41055-2023 artfynd.xlsx
+++ b/artfynd/A 41055-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41055-2023 artfynd.xlsx
+++ b/artfynd/A 41055-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61957351</v>
+        <v>32299</v>
       </c>
       <c r="B2" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101268</v>
+        <v>100077</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Margaritifera margaritifera</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,28 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 15, Vb</t>
+          <t>Finnforsån, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754018.3442604135</v>
+        <v>753849</v>
       </c>
       <c r="R2" t="n">
-        <v>7191507.269111481</v>
+        <v>7191558</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lokal 15. Längd= 14m. Bredd= 3,2m. Antal levande= 182 st. Antal döda= 3 st. Minsta mussla= 46mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Inventerare:Frida Sandström, Andreas Garpebring, fisk, vägtrumma + 30 m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,31 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Emil Larsson</t>
+          <t>Via Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Miljöövervakning flodpärlmussla</t>
+          <t>Inventering av utter Västerbottens län 2005-2007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61957347</v>
+        <v>61957346</v>
       </c>
       <c r="B3" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -848,14 +825,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 11, Vb</t>
+          <t>Finnforsån Lokal 10, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754253.5519666261</v>
+        <v>754358</v>
       </c>
       <c r="R3" t="n">
-        <v>7191320.87008727</v>
+        <v>7191201</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -885,24 +862,14 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lokal 11. Längd= 14,5m. Bredd= 1,7m. Antal levande= 1279 st. Antal döda= 1 st. Minsta mussla= Info saknas. Mörkt i vattnet gjorde det svårt att se För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Lokal 10. Längd= 16m. Bredd= 2m. Antal levande= 147 st. Antal döda= 0 st. Minsta mussla= 33mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61957360</v>
+        <v>61957347</v>
       </c>
       <c r="B4" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,7 +930,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -977,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 9, Vb</t>
+          <t>Finnforsån Lokal 11, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754358.2282767468</v>
+        <v>754254</v>
       </c>
       <c r="R4" t="n">
-        <v>7191129.421903082</v>
+        <v>7191321</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1014,24 +976,14 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lokal 9. Längd= 15,5m. Bredd= 2,5m. Antal levande= 118 st. Antal döda= 0 st. Minsta mussla= Info saknas.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Lokal 11. Längd= 14,5m. Bredd= 1,7m. Antal levande= 1279 st. Antal döda= 1 st. Minsta mussla= Info saknas. Mörkt i vattnet gjorde det svårt att se För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1017,7 @@
         <v>61957348</v>
       </c>
       <c r="B5" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754166.658196805</v>
+        <v>754167</v>
       </c>
       <c r="R5" t="n">
-        <v>7191419.026977272</v>
+        <v>7191419</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1143,19 +1090,9 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1191,15 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61957346</v>
+        <v>61957349</v>
       </c>
       <c r="B6" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1158,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1235,14 +1167,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 10, Vb</t>
+          <t>Finnforsån Lokal 13, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754358.139431505</v>
+        <v>754087</v>
       </c>
       <c r="R6" t="n">
-        <v>7191201.476249084</v>
+        <v>7191453</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1272,24 +1204,14 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-06</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lokal 10. Längd= 16m. Bredd= 2m. Antal levande= 147 st. Antal döda= 0 st. Minsta mussla= 33mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Lokal 13. Längd= 15,5m. Bredd= 2,7m. Antal levande= 78 st. Antal döda= 0 st. Minsta mussla= 68mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,15 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61981830</v>
+        <v>61957350</v>
       </c>
       <c r="B7" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,19 +1272,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 7, Vb</t>
+          <t>Finnforsån Lokal 14, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754382.2516881071</v>
+        <v>754048</v>
       </c>
       <c r="R7" t="n">
-        <v>7191129.740426734</v>
+        <v>7191481</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1394,27 +1315,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lokal 7. Längd= 15m. Bredd= 1,9m. Antal levande= 54 st. Antal döda= 0 st. Minsta mussla= 52 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+          <t>Lokal 14. Längd= 16,5m. Bredd= 2,6m. Antal levande= 185 st. Antal döda= 0 st. Minsta mussla= 56mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,19 +1348,18 @@
           <t>Via Emil Larsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61981835</v>
+        <v>61957351</v>
       </c>
       <c r="B8" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,19 +1386,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 2, Vb</t>
+          <t>Finnforsån Lokal 15, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754054.5362627876</v>
+        <v>754018</v>
       </c>
       <c r="R8" t="n">
-        <v>7191490.601610618</v>
+        <v>7191507</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1515,27 +1429,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lokal 2. Längd= 15m. Bredd= 2,3m. Antal levande= 133 st. Antal döda= 0 st. Minsta mussla= 53 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+          <t>Lokal 15. Längd= 14m. Bredd= 3,2m. Antal levande= 182 st. Antal döda= 3 st. Minsta mussla= 46mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,19 +1462,18 @@
           <t>Via Emil Larsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61981833</v>
+        <v>61957360</v>
       </c>
       <c r="B9" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,19 +1500,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 3, Vb</t>
+          <t>Finnforsån Lokal 9, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754126.0328051922</v>
+        <v>754358</v>
       </c>
       <c r="R9" t="n">
-        <v>7191457.621202857</v>
+        <v>7191129</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1636,27 +1543,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lokal 3. Längd= 15m. Bredd= 2,8m. Antal levande= 152 st. Antal döda= 1 st. Minsta mussla= 71 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+          <t>Lokal 9. Längd= 15,5m. Bredd= 2,5m. Antal levande= 118 st. Antal döda= 0 st. Minsta mussla= Info saknas.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,19 +1576,18 @@
           <t>Via Emil Larsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61981832</v>
+        <v>61981830</v>
       </c>
       <c r="B10" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,19 +1614,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>54</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 4, Vb</t>
+          <t>Finnforsån Lokal 7, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754216.4416899851</v>
+        <v>754382</v>
       </c>
       <c r="R10" t="n">
-        <v>7191419.38008659</v>
+        <v>7191130</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1760,24 +1656,14 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2006-12-31</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lokal 4. Längd= 15m. Bredd= 2,2m. Antal levande= 324 st. Antal döda= 1 st. Minsta mussla= 70 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+          <t>Lokal 7. Längd= 15m. Bredd= 1,9m. Antal levande= 54 st. Antal döda= 0 st. Minsta mussla= 52 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,6 +1687,536 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>61981831</v>
+      </c>
+      <c r="B11" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 6, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>754371</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7191212</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lokal 6. Längd= 15m. Bredd= 2,1m. Antal levande= 78 st. Antal döda= 2 st. Minsta mussla= 42 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>61981832</v>
+      </c>
+      <c r="B12" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 4, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>754216</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7191419</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lokal 4. Längd= 15m. Bredd= 2,2m. Antal levande= 324 st. Antal döda= 1 st. Minsta mussla= 70 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>61981833</v>
+      </c>
+      <c r="B13" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 3, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>754126</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7191458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lokal 3. Längd= 15m. Bredd= 2,8m. Antal levande= 152 st. Antal döda= 1 st. Minsta mussla= 71 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>61981835</v>
+      </c>
+      <c r="B14" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 2, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>754055</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7191491</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lokal 2. Längd= 15m. Bredd= 2,3m. Antal levande= 133 st. Antal döda= 0 st. Minsta mussla= 53 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>61981837</v>
+      </c>
+      <c r="B15" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 1, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>754033</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7191512</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lokal 1. Längd= 15m. Bredd= 3m. Antal levande= 26 st. Antal döda= 5 st. Minsta mussla= 43 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41055-2023 artfynd.xlsx
+++ b/artfynd/A 41055-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Inventering av utter Västerbottens län 2005-2007</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/32299</t>
         </is>
       </c>
     </row>
@@ -897,6 +907,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957346</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957348</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957349</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957350</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957351</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957360</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981830</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1793,6 +1843,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981831</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981832</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981833</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2111,6 +2176,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981835</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,8 +2287,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>